--- a/ig/nr/3.0.1/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/nr/3.0.1/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$92</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3608" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3570" uniqueCount="654">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-26T08:11:02+00:00</t>
+    <t>2023-04-26T08:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -326,6 +326,10 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -400,10 +404,6 @@
     <t>Meta.versionId</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
     <t>Observation.meta.lastUpdated</t>
   </si>
   <si>
@@ -456,14 +456,7 @@
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
-</t>
-  </si>
-  <si>
     <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>Observation.meta.profile:MesObservationWaistCircumference</t>
   </si>
   <si>
     <t>Observation.meta.security</t>
@@ -2378,12 +2371,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP93"/>
+  <dimension ref="A1:AP92"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="57.98046875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.3046875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="49.3046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="34.4453125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="27.03125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2805,7 +2798,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>88</v>
@@ -2889,7 +2882,7 @@
         <v>100</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>78</v>
@@ -2901,7 +2894,7 @@
         <v>78</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO4" t="s" s="2">
         <v>78</v>
@@ -2912,10 +2905,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2938,13 +2931,13 @@
         <v>78</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2995,7 +2988,7 @@
         <v>78</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
@@ -3019,7 +3012,7 @@
         <v>78</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>78</v>
@@ -3030,14 +3023,14 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -3056,16 +3049,16 @@
         <v>78</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -3103,19 +3096,19 @@
         <v>78</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
@@ -3127,7 +3120,7 @@
         <v>100</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>78</v>
@@ -3139,7 +3132,7 @@
         <v>78</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>78</v>
@@ -3150,10 +3143,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -3179,13 +3172,13 @@
         <v>90</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3235,7 +3228,7 @@
         <v>78</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -3247,7 +3240,7 @@
         <v>100</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>78</v>
@@ -3259,7 +3252,7 @@
         <v>78</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>78</v>
@@ -3367,7 +3360,7 @@
         <v>100</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>78</v>
@@ -3379,7 +3372,7 @@
         <v>78</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>78</v>
@@ -3487,7 +3480,7 @@
         <v>100</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>78</v>
@@ -3499,7 +3492,7 @@
         <v>78</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>78</v>
@@ -3521,7 +3514,7 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>77</v>
@@ -3583,17 +3576,19 @@
         <v>78</v>
       </c>
       <c r="AB10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF10" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="AC10" s="2"/>
-      <c r="AD10" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE10" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AF10" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -3605,7 +3600,7 @@
         <v>100</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>78</v>
@@ -3617,7 +3612,7 @@
         <v>78</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>78</v>
@@ -3628,26 +3623,24 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>7</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>78</v>
@@ -3656,16 +3649,16 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3673,7 +3666,7 @@
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="S11" t="s" s="2">
         <v>78</v>
@@ -3691,13 +3684,13 @@
         <v>78</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>78</v>
+        <v>149</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>78</v>
@@ -3715,7 +3708,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -3727,7 +3720,7 @@
         <v>100</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>78</v>
@@ -3736,10 +3729,10 @@
         <v>78</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>78</v>
@@ -3750,10 +3743,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3776,16 +3769,16 @@
         <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3811,13 +3804,13 @@
         <v>78</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>78</v>
@@ -3835,7 +3828,7 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -3847,7 +3840,7 @@
         <v>100</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>78</v>
@@ -3856,10 +3849,10 @@
         <v>78</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>78</v>
@@ -3870,10 +3863,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3884,28 +3877,28 @@
         <v>76</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3931,13 +3924,13 @@
         <v>78</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>160</v>
+        <v>78</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>78</v>
@@ -3955,19 +3948,19 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>78</v>
@@ -3976,10 +3969,10 @@
         <v>78</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>78</v>
@@ -3990,10 +3983,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4010,22 +4003,22 @@
         <v>78</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4051,13 +4044,13 @@
         <v>78</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>78</v>
@@ -4075,7 +4068,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -4087,7 +4080,7 @@
         <v>100</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>78</v>
@@ -4099,7 +4092,7 @@
         <v>78</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>78</v>
@@ -4110,14 +4103,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>78</v>
+        <v>176</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4136,16 +4129,16 @@
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4171,13 +4164,13 @@
         <v>78</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>173</v>
+        <v>78</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>175</v>
+        <v>78</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>78</v>
@@ -4195,7 +4188,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -4207,7 +4200,7 @@
         <v>100</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>78</v>
@@ -4219,7 +4212,7 @@
         <v>78</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>107</v>
+        <v>182</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>78</v>
@@ -4230,21 +4223,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>78</v>
@@ -4256,16 +4249,16 @@
         <v>78</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4315,19 +4308,19 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>78</v>
@@ -4339,7 +4332,7 @@
         <v>78</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>184</v>
+        <v>102</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>78</v>
@@ -4350,14 +4343,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>186</v>
+        <v>110</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4376,16 +4369,16 @@
         <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>187</v>
+        <v>111</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>112</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>190</v>
+        <v>114</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4423,19 +4416,19 @@
         <v>78</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -4444,10 +4437,10 @@
         <v>77</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>78</v>
@@ -4459,7 +4452,7 @@
         <v>78</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>78</v>
@@ -4470,21 +4463,23 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="D18" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>78</v>
@@ -4496,17 +4491,15 @@
         <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>110</v>
+        <v>195</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>111</v>
+        <v>196</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -4543,19 +4536,19 @@
         <v>78</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -4567,7 +4560,7 @@
         <v>100</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>78</v>
@@ -4579,7 +4572,7 @@
         <v>78</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>78</v>
@@ -4590,13 +4583,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>78</v>
@@ -4618,13 +4611,13 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4675,7 +4668,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -4687,7 +4680,7 @@
         <v>100</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>78</v>
@@ -4699,7 +4692,7 @@
         <v>78</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>78</v>
@@ -4710,44 +4703,46 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>202</v>
+        <v>111</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>78</v>
       </c>
@@ -4783,19 +4778,19 @@
         <v>78</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -4807,7 +4802,7 @@
         <v>100</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>78</v>
@@ -4819,7 +4814,7 @@
         <v>78</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>78</v>
@@ -4830,14 +4825,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4850,25 +4845,23 @@
         <v>78</v>
       </c>
       <c r="I21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="J21" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K21" t="s" s="2">
-        <v>110</v>
+        <v>209</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>78</v>
@@ -4905,19 +4898,19 @@
         <v>78</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -4929,22 +4922,22 @@
         <v>100</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>78</v>
+        <v>213</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>78</v>
+        <v>214</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>101</v>
+        <v>215</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>78</v>
@@ -4952,14 +4945,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4978,17 +4971,19 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="O22" t="s" s="2">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -5037,7 +5032,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -5049,22 +5044,22 @@
         <v>100</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>78</v>
@@ -5072,14 +5067,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5098,20 +5093,18 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>78</v>
       </c>
@@ -5159,7 +5152,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -5171,19 +5164,19 @@
         <v>100</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>78</v>
@@ -5194,44 +5187,46 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>231</v>
+        <v>78</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>232</v>
+        <v>167</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
       </c>
@@ -5255,13 +5250,13 @@
         <v>78</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>78</v>
@@ -5279,34 +5274,34 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>226</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>78</v>
+        <v>246</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>78</v>
+        <v>249</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>78</v>
@@ -5314,10 +5309,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5328,31 +5323,31 @@
         <v>88</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>89</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>169</v>
+        <v>251</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -5377,58 +5372,56 @@
         <v>78</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>244</v>
+        <v>171</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>247</v>
+        <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>78</v>
@@ -5436,12 +5429,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>78</v>
       </c>
@@ -5450,7 +5445,7 @@
         <v>88</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>89</v>
@@ -5462,19 +5457,19 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -5499,29 +5494,31 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="AC26" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -5533,7 +5530,7 @@
         <v>100</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
@@ -5542,13 +5539,13 @@
         <v>78</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>78</v>
@@ -5559,23 +5556,21 @@
         <v>264</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C27" t="s" s="2">
         <v>265</v>
       </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>78</v>
@@ -5584,20 +5579,16 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
       </c>
@@ -5621,13 +5612,13 @@
         <v>78</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>173</v>
+        <v>78</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>258</v>
+        <v>78</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>259</v>
+        <v>78</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>78</v>
@@ -5645,19 +5636,19 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>252</v>
+        <v>107</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>78</v>
@@ -5666,13 +5657,13 @@
         <v>78</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>261</v>
+        <v>78</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>262</v>
+        <v>108</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>263</v>
+        <v>78</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>78</v>
@@ -5687,14 +5678,14 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>78</v>
@@ -5706,15 +5697,17 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -5751,31 +5744,31 @@
         <v>78</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>78</v>
@@ -5787,7 +5780,7 @@
         <v>78</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>78</v>
@@ -5805,37 +5798,39 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>111</v>
+        <v>270</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>112</v>
+        <v>271</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
       </c>
@@ -5871,19 +5866,19 @@
         <v>78</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>117</v>
+        <v>274</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -5895,7 +5890,7 @@
         <v>100</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>78</v>
@@ -5904,10 +5899,10 @@
         <v>78</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>101</v>
+        <v>276</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>78</v>
@@ -5918,10 +5913,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5929,35 +5924,31 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G30" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G30" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="H30" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>78</v>
       </c>
@@ -6005,19 +5996,19 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>276</v>
+        <v>107</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>78</v>
@@ -6026,10 +6017,10 @@
         <v>78</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>277</v>
+        <v>78</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>278</v>
+        <v>108</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>78</v>
@@ -6047,14 +6038,14 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>78</v>
@@ -6066,15 +6057,17 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -6111,31 +6104,31 @@
         <v>78</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>78</v>
@@ -6147,7 +6140,7 @@
         <v>78</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>78</v>
@@ -6165,43 +6158,45 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>78</v>
+        <v>287</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>78</v>
@@ -6231,31 +6226,31 @@
         <v>78</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>78</v>
@@ -6264,10 +6259,10 @@
         <v>78</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>101</v>
+        <v>290</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>78</v>
@@ -6278,10 +6273,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6289,13 +6284,13 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>78</v>
@@ -6304,26 +6299,24 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>289</v>
+        <v>78</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>78</v>
@@ -6365,7 +6358,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -6377,7 +6370,7 @@
         <v>100</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>78</v>
@@ -6386,10 +6379,10 @@
         <v>78</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>78</v>
@@ -6400,10 +6393,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6411,13 +6404,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>78</v>
@@ -6426,24 +6419,26 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>103</v>
+        <v>167</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>78</v>
+        <v>305</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>78</v>
@@ -6485,7 +6480,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -6497,7 +6492,7 @@
         <v>100</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>78</v>
@@ -6506,10 +6501,10 @@
         <v>78</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>78</v>
@@ -6520,10 +6515,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6531,13 +6526,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>78</v>
@@ -6546,26 +6541,26 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="O35" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>307</v>
+        <v>78</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>78</v>
@@ -6607,7 +6602,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -6619,7 +6614,7 @@
         <v>100</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>78</v>
@@ -6628,10 +6623,10 @@
         <v>78</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>78</v>
@@ -6642,10 +6637,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6668,19 +6663,19 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6729,7 +6724,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -6741,7 +6736,7 @@
         <v>100</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>78</v>
@@ -6750,10 +6745,10 @@
         <v>78</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>78</v>
@@ -6764,10 +6759,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6790,19 +6785,19 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>321</v>
+        <v>104</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -6851,7 +6846,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -6863,7 +6858,7 @@
         <v>100</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>78</v>
@@ -6872,10 +6867,10 @@
         <v>78</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>78</v>
@@ -6886,24 +6881,24 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>78</v>
+        <v>337</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>78</v>
@@ -6912,19 +6907,19 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>103</v>
+        <v>251</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -6934,7 +6929,7 @@
         <v>78</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>78</v>
@@ -6949,13 +6944,13 @@
         <v>78</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>78</v>
+        <v>343</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>78</v>
+        <v>344</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>78</v>
@@ -6973,10 +6968,10 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>88</v>
@@ -6985,37 +6980,37 @@
         <v>100</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>78</v>
+        <v>345</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>78</v>
+        <v>346</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>78</v>
+        <v>349</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>78</v>
+        <v>350</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>339</v>
+        <v>78</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7034,19 +7029,19 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>253</v>
+        <v>352</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -7056,7 +7051,7 @@
         <v>78</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>78</v>
@@ -7071,13 +7066,13 @@
         <v>78</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>345</v>
+        <v>78</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>346</v>
+        <v>78</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>78</v>
@@ -7095,10 +7090,10 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>88</v>
@@ -7107,33 +7102,33 @@
         <v>100</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>348</v>
+        <v>78</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>352</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7141,13 +7136,13 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>78</v>
@@ -7156,20 +7151,18 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>78</v>
       </c>
@@ -7217,34 +7210,34 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>359</v>
+        <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>78</v>
@@ -7252,21 +7245,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>78</v>
+        <v>368</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>78</v>
@@ -7278,18 +7271,20 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>78</v>
       </c>
@@ -7337,34 +7332,34 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>78</v>
+        <v>374</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>78</v>
@@ -7372,24 +7367,24 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>78</v>
@@ -7398,19 +7393,19 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -7459,7 +7454,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -7468,25 +7463,25 @@
         <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>100</v>
+        <v>385</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>226</v>
+        <v>386</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>78</v>
@@ -7494,24 +7489,24 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>381</v>
+        <v>78</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>78</v>
@@ -7520,20 +7515,18 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>382</v>
+        <v>126</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>386</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>78</v>
       </c>
@@ -7581,7 +7574,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -7590,25 +7583,25 @@
         <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>387</v>
+        <v>100</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>388</v>
+        <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>78</v>
@@ -7616,10 +7609,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7630,7 +7623,7 @@
         <v>76</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>78</v>
@@ -7642,18 +7635,20 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>126</v>
+        <v>399</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
       </c>
@@ -7701,34 +7696,34 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>78</v>
+        <v>403</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>78</v>
@@ -7736,10 +7731,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7750,10 +7745,10 @@
         <v>76</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>78</v>
@@ -7762,19 +7757,19 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>224</v>
+        <v>410</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -7811,59 +7806,59 @@
         <v>78</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>78</v>
+        <v>413</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>100</v>
+        <v>414</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>226</v>
+        <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>405</v>
+        <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>78</v>
+        <v>415</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>408</v>
+        <v>78</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>78</v>
+        <v>418</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C46" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="D46" t="s" s="2">
         <v>78</v>
       </c>
@@ -7884,19 +7879,19 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -7906,7 +7901,7 @@
         <v>78</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>78</v>
+        <v>421</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>78</v>
@@ -7933,17 +7928,19 @@
         <v>78</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="AC46" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>415</v>
+        <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7952,40 +7949,38 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AJ46" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>420</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>78</v>
       </c>
@@ -7997,29 +7992,25 @@
         <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>410</v>
+        <v>104</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>411</v>
+        <v>105</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>78</v>
       </c>
@@ -8028,7 +8019,7 @@
         <v>78</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>423</v>
+        <v>78</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>78</v>
@@ -8067,7 +8058,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>409</v>
+        <v>107</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -8076,28 +8067,28 @@
         <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>416</v>
+        <v>78</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>417</v>
+        <v>78</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>418</v>
+        <v>78</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>419</v>
+        <v>108</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" hidden="true">
@@ -8109,14 +8100,14 @@
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>78</v>
@@ -8128,15 +8119,17 @@
         <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -8173,31 +8166,31 @@
         <v>78</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>78</v>
@@ -8209,7 +8202,7 @@
         <v>78</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>78</v>
@@ -8227,14 +8220,14 @@
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>78</v>
@@ -8243,21 +8236,23 @@
         <v>78</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>110</v>
+        <v>428</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>111</v>
+        <v>429</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>112</v>
+        <v>430</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
       </c>
@@ -8293,31 +8288,31 @@
         <v>78</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>117</v>
+        <v>433</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>78</v>
@@ -8326,10 +8321,10 @@
         <v>78</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>78</v>
+        <v>434</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>101</v>
+        <v>435</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>78</v>
@@ -8340,10 +8335,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8360,30 +8355,32 @@
         <v>78</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>430</v>
+        <v>167</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>433</v>
+        <v>303</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q50" s="2"/>
+      <c r="Q50" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="R50" t="s" s="2">
         <v>78</v>
       </c>
@@ -8403,13 +8400,13 @@
         <v>78</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>78</v>
+        <v>442</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>78</v>
+        <v>443</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>78</v>
@@ -8427,7 +8424,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -8439,7 +8436,7 @@
         <v>100</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>78</v>
@@ -8448,10 +8445,10 @@
         <v>78</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>78</v>
@@ -8462,10 +8459,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8482,32 +8479,30 @@
         <v>78</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q51" t="s" s="2">
-        <v>443</v>
-      </c>
+      <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
         <v>78</v>
       </c>
@@ -8527,13 +8522,13 @@
         <v>78</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>444</v>
+        <v>78</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>445</v>
+        <v>78</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>78</v>
@@ -8551,7 +8546,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -8563,7 +8558,7 @@
         <v>100</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>78</v>
@@ -8572,10 +8567,10 @@
         <v>78</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>78</v>
@@ -8586,10 +8581,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8597,7 +8592,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>88</v>
@@ -8612,19 +8607,19 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>305</v>
+        <v>459</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -8673,7 +8668,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -8682,10 +8677,10 @@
         <v>88</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>100</v>
+        <v>462</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>78</v>
@@ -8694,10 +8689,10 @@
         <v>78</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>78</v>
@@ -8708,10 +8703,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8734,19 +8729,19 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8795,7 +8790,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -8804,10 +8799,10 @@
         <v>88</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>464</v>
+        <v>100</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>78</v>
@@ -8816,10 +8811,10 @@
         <v>78</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>78</v>
@@ -8830,10 +8825,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8841,34 +8836,34 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>169</v>
+        <v>251</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8893,13 +8888,13 @@
         <v>78</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>78</v>
+        <v>477</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>78</v>
+        <v>478</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8926,10 +8921,10 @@
         <v>88</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>100</v>
+        <v>479</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>78</v>
@@ -8938,10 +8933,10 @@
         <v>78</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>455</v>
+        <v>102</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>78</v>
@@ -8952,10 +8947,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8969,7 +8964,7 @@
         <v>88</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>78</v>
@@ -8978,20 +8973,16 @@
         <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>475</v>
+        <v>105</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>78</v>
       </c>
@@ -9015,13 +9006,13 @@
         <v>78</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>479</v>
+        <v>78</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>480</v>
+        <v>78</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>78</v>
@@ -9039,7 +9030,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>474</v>
+        <v>107</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -9048,10 +9039,10 @@
         <v>88</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>481</v>
+        <v>78</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>78</v>
@@ -9060,10 +9051,10 @@
         <v>78</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>482</v>
+        <v>108</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>78</v>
@@ -9074,21 +9065,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>78</v>
@@ -9100,15 +9091,17 @@
         <v>78</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -9145,31 +9138,31 @@
         <v>78</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>78</v>
@@ -9181,7 +9174,7 @@
         <v>78</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>78</v>
@@ -9192,14 +9185,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9215,21 +9208,23 @@
         <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>111</v>
+        <v>270</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>112</v>
+        <v>271</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
       </c>
@@ -9265,19 +9260,19 @@
         <v>78</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>117</v>
+        <v>274</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -9289,7 +9284,7 @@
         <v>100</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>78</v>
@@ -9298,10 +9293,10 @@
         <v>78</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>101</v>
+        <v>276</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>78</v>
@@ -9312,10 +9307,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9326,7 +9321,7 @@
         <v>76</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>78</v>
@@ -9335,23 +9330,19 @@
         <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>78</v>
       </c>
@@ -9399,19 +9390,19 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>276</v>
+        <v>107</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>78</v>
@@ -9420,10 +9411,10 @@
         <v>78</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>277</v>
+        <v>78</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>278</v>
+        <v>108</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>78</v>
@@ -9434,21 +9425,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>78</v>
@@ -9460,15 +9451,17 @@
         <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -9505,31 +9498,31 @@
         <v>78</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>78</v>
@@ -9541,7 +9534,7 @@
         <v>78</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>78</v>
@@ -9552,21 +9545,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -9575,21 +9568,23 @@
         <v>78</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
       </c>
@@ -9625,31 +9620,31 @@
         <v>78</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>78</v>
@@ -9658,10 +9653,10 @@
         <v>78</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>101</v>
+        <v>290</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>78</v>
@@ -9672,10 +9667,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9683,7 +9678,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>88</v>
@@ -9698,20 +9693,18 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>78</v>
       </c>
@@ -9759,7 +9752,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -9771,7 +9764,7 @@
         <v>100</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>78</v>
@@ -9780,10 +9773,10 @@
         <v>78</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>78</v>
@@ -9794,10 +9787,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9805,7 +9798,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>88</v>
@@ -9820,18 +9813,20 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>103</v>
+        <v>167</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>78</v>
       </c>
@@ -9879,7 +9874,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -9891,7 +9886,7 @@
         <v>100</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>78</v>
@@ -9900,10 +9895,10 @@
         <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>78</v>
@@ -9914,10 +9909,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9925,7 +9920,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>88</v>
@@ -9940,19 +9935,19 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N63" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M63" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="O63" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -10001,7 +9996,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -10013,7 +10008,7 @@
         <v>100</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>78</v>
@@ -10022,10 +10017,10 @@
         <v>78</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -10036,10 +10031,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10062,19 +10057,19 @@
         <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -10123,7 +10118,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -10135,7 +10130,7 @@
         <v>100</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>78</v>
@@ -10144,10 +10139,10 @@
         <v>78</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>78</v>
@@ -10158,10 +10153,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10184,19 +10179,19 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>321</v>
+        <v>104</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
@@ -10245,7 +10240,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -10257,7 +10252,7 @@
         <v>100</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>78</v>
@@ -10266,10 +10261,10 @@
         <v>78</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>78</v>
@@ -10280,21 +10275,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>78</v>
+        <v>493</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>78</v>
@@ -10303,22 +10298,22 @@
         <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>103</v>
+        <v>251</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>331</v>
+        <v>494</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>332</v>
+        <v>495</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>333</v>
+        <v>496</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>334</v>
+        <v>497</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -10343,13 +10338,13 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>78</v>
+        <v>498</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>78</v>
+        <v>499</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -10367,49 +10362,49 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>335</v>
+        <v>492</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>78</v>
+        <v>500</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>336</v>
+        <v>501</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>337</v>
+        <v>502</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>78</v>
+        <v>503</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>495</v>
+        <v>78</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10428,19 +10423,19 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>253</v>
+        <v>505</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -10465,13 +10460,13 @@
         <v>78</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>500</v>
+        <v>78</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>501</v>
+        <v>78</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>78</v>
@@ -10489,7 +10484,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -10501,33 +10496,33 @@
         <v>100</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>502</v>
+        <v>78</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>505</v>
+        <v>78</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10538,7 +10533,7 @@
         <v>76</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>78</v>
@@ -10550,20 +10545,18 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>507</v>
+        <v>251</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>511</v>
-      </c>
+        <v>515</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>78</v>
       </c>
@@ -10587,13 +10580,13 @@
         <v>78</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>78</v>
+        <v>516</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>78</v>
+        <v>517</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>78</v>
@@ -10611,45 +10604,45 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>78</v>
+        <v>518</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>78</v>
+        <v>521</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10672,18 +10665,20 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>526</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
       </c>
@@ -10707,13 +10702,13 @@
         <v>78</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>78</v>
@@ -10731,7 +10726,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -10743,33 +10738,33 @@
         <v>100</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>520</v>
+        <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>523</v>
+        <v>78</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10792,20 +10787,18 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>253</v>
+        <v>532</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>528</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>78</v>
       </c>
@@ -10829,13 +10822,13 @@
         <v>78</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>529</v>
+        <v>78</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>530</v>
+        <v>78</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>78</v>
@@ -10853,7 +10846,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -10865,33 +10858,33 @@
         <v>100</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>78</v>
+        <v>536</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>78</v>
+        <v>539</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10914,16 +10907,16 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10973,7 +10966,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10985,33 +10978,33 @@
         <v>100</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>541</v>
+        <v>548</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11022,7 +11015,7 @@
         <v>76</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>78</v>
@@ -11034,18 +11027,20 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="O72" s="2"/>
+        <v>553</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>554</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
       </c>
@@ -11093,45 +11088,45 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>226</v>
+        <v>555</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>547</v>
+        <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>550</v>
+        <v>78</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11142,7 +11137,7 @@
         <v>76</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>78</v>
@@ -11154,20 +11149,16 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>552</v>
+        <v>104</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>553</v>
+        <v>105</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>556</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>78</v>
       </c>
@@ -11215,19 +11206,19 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>551</v>
+        <v>107</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>557</v>
+        <v>78</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>78</v>
@@ -11236,10 +11227,10 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>558</v>
+        <v>78</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>559</v>
+        <v>108</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>78</v>
@@ -11250,21 +11241,21 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>78</v>
@@ -11276,15 +11267,17 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>78</v>
@@ -11321,31 +11314,31 @@
         <v>78</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>78</v>
@@ -11357,7 +11350,7 @@
         <v>78</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>78</v>
@@ -11368,14 +11361,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>109</v>
+        <v>561</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -11388,24 +11381,26 @@
         <v>78</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>111</v>
+        <v>562</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>112</v>
+        <v>563</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O75" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
       </c>
@@ -11441,19 +11436,19 @@
         <v>78</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>117</v>
+        <v>564</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -11465,7 +11460,7 @@
         <v>100</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>78</v>
@@ -11477,7 +11472,7 @@
         <v>78</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>78</v>
@@ -11488,46 +11483,44 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>563</v>
+        <v>78</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>110</v>
+        <v>566</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>78</v>
       </c>
@@ -11575,19 +11568,19 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>100</v>
+        <v>570</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>118</v>
+        <v>571</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>78</v>
@@ -11596,10 +11589,10 @@
         <v>78</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>78</v>
+        <v>572</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>101</v>
+        <v>573</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>78</v>
@@ -11610,10 +11603,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11636,16 +11629,16 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11695,7 +11688,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -11704,22 +11697,22 @@
         <v>88</v>
       </c>
       <c r="AI77" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="AJ77" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>574</v>
-      </c>
       <c r="AN77" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>78</v>
@@ -11730,10 +11723,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11756,18 +11749,20 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>568</v>
+        <v>251</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>581</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>582</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>78</v>
       </c>
@@ -11791,13 +11786,13 @@
         <v>78</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>78</v>
+        <v>583</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>78</v>
+        <v>584</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>78</v>
@@ -11815,7 +11810,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -11824,22 +11819,22 @@
         <v>88</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>572</v>
+        <v>100</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>573</v>
+        <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>78</v>
+        <v>585</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>579</v>
+        <v>502</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>78</v>
@@ -11850,10 +11845,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11864,7 +11859,7 @@
         <v>76</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>78</v>
@@ -11876,19 +11871,19 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11913,13 +11908,13 @@
         <v>78</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>78</v>
@@ -11937,31 +11932,31 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>78</v>
@@ -11972,10 +11967,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11986,7 +11981,7 @@
         <v>76</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>78</v>
@@ -11998,19 +11993,19 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>253</v>
+        <v>595</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>78</v>
@@ -12035,55 +12030,55 @@
         <v>78</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="Z80" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>589</v>
-      </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>124</v>
+        <v>600</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>587</v>
+        <v>78</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>588</v>
+        <v>601</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>504</v>
+        <v>602</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>78</v>
@@ -12094,10 +12089,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12120,20 +12115,18 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>597</v>
+        <v>104</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>601</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>78</v>
       </c>
@@ -12181,7 +12174,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -12193,7 +12186,7 @@
         <v>100</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>602</v>
+        <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>78</v>
@@ -12202,10 +12195,10 @@
         <v>78</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>603</v>
+        <v>572</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>78</v>
@@ -12216,10 +12209,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12230,7 +12223,7 @@
         <v>76</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>78</v>
@@ -12239,19 +12232,19 @@
         <v>78</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>103</v>
+        <v>608</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>305</v>
+        <v>611</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12301,19 +12294,19 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>78</v>
@@ -12322,10 +12315,10 @@
         <v>78</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>574</v>
+        <v>612</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>78</v>
@@ -12336,10 +12329,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12362,16 +12355,16 @@
         <v>89</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12421,7 +12414,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -12433,7 +12426,7 @@
         <v>100</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>78</v>
@@ -12442,10 +12435,10 @@
         <v>78</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>78</v>
@@ -12456,10 +12449,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12473,7 +12466,7 @@
         <v>77</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>78</v>
@@ -12482,18 +12475,20 @@
         <v>89</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>617</v>
+        <v>550</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="O84" s="2"/>
+        <v>622</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>623</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
       </c>
@@ -12541,7 +12536,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -12553,7 +12548,7 @@
         <v>100</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>226</v>
+        <v>624</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>78</v>
@@ -12562,10 +12557,10 @@
         <v>78</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>78</v>
@@ -12576,10 +12571,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12590,32 +12585,28 @@
         <v>76</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>552</v>
+        <v>104</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>623</v>
+        <v>105</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>625</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>78</v>
       </c>
@@ -12663,19 +12654,19 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>622</v>
+        <v>107</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>626</v>
+        <v>78</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>78</v>
@@ -12684,10 +12675,10 @@
         <v>78</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>627</v>
+        <v>78</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>628</v>
+        <v>108</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>78</v>
@@ -12698,21 +12689,21 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>78</v>
@@ -12724,15 +12715,17 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>78</v>
@@ -12769,31 +12762,31 @@
         <v>78</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>78</v>
@@ -12805,7 +12798,7 @@
         <v>78</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>78</v>
@@ -12816,14 +12809,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>109</v>
+        <v>561</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12836,24 +12829,26 @@
         <v>78</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>111</v>
+        <v>562</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>112</v>
+        <v>563</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O87" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>78</v>
       </c>
@@ -12889,19 +12884,19 @@
         <v>78</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>117</v>
+        <v>564</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -12913,7 +12908,7 @@
         <v>100</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>78</v>
@@ -12925,7 +12920,7 @@
         <v>78</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>78</v>
@@ -12936,45 +12931,45 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>563</v>
+        <v>78</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J88" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>110</v>
+        <v>251</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>564</v>
+        <v>631</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>565</v>
+        <v>632</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>113</v>
+        <v>633</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>208</v>
+        <v>634</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>78</v>
@@ -12999,13 +12994,13 @@
         <v>78</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>78</v>
+        <v>343</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>78</v>
+        <v>344</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>78</v>
@@ -13023,34 +13018,34 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>566</v>
+        <v>630</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>78</v>
+        <v>635</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>78</v>
+        <v>347</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>101</v>
+        <v>348</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>78</v>
+        <v>349</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>78</v>
@@ -13058,10 +13053,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13069,7 +13064,7 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>88</v>
@@ -13084,19 +13079,19 @@
         <v>89</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>253</v>
+        <v>637</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>636</v>
+        <v>411</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>78</v>
@@ -13121,13 +13116,13 @@
         <v>78</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>149</v>
+        <v>242</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>345</v>
+        <v>641</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>346</v>
+        <v>642</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>78</v>
@@ -13145,45 +13140,45 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>100</v>
+        <v>643</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>349</v>
+        <v>416</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>350</v>
+        <v>417</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>351</v>
+        <v>78</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>78</v>
+        <v>418</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13203,22 +13198,22 @@
         <v>78</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>639</v>
+        <v>251</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>413</v>
+        <v>476</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>78</v>
@@ -13243,13 +13238,13 @@
         <v>78</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>244</v>
+        <v>147</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>643</v>
+        <v>477</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>644</v>
+        <v>478</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>78</v>
@@ -13267,7 +13262,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -13276,50 +13271,50 @@
         <v>88</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>646</v>
+        <v>78</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>418</v>
+        <v>102</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>419</v>
+        <v>480</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>78</v>
+        <v>493</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>78</v>
@@ -13328,19 +13323,19 @@
         <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>648</v>
+        <v>494</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>649</v>
+        <v>495</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>650</v>
+        <v>496</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
@@ -13365,13 +13360,13 @@
         <v>78</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>479</v>
+        <v>498</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>480</v>
+        <v>499</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>78</v>
@@ -13389,49 +13384,49 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>651</v>
+        <v>100</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>78</v>
+        <v>500</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>101</v>
+        <v>501</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>78</v>
+        <v>503</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>495</v>
+        <v>78</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13450,19 +13445,19 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>253</v>
+        <v>79</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>496</v>
+        <v>652</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>497</v>
+        <v>653</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>498</v>
+        <v>553</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>499</v>
+        <v>554</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>78</v>
@@ -13487,13 +13482,13 @@
         <v>78</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>500</v>
+        <v>78</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>501</v>
+        <v>78</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>78</v>
@@ -13511,7 +13506,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -13520,154 +13515,32 @@
         <v>77</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>502</v>
+        <v>78</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>503</v>
+        <v>556</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>504</v>
+        <v>557</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="93" hidden="true">
-      <c r="A93" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E93" s="2"/>
-      <c r="F93" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="P93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q93" s="2"/>
-      <c r="R93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP93" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP93">
+  <autoFilter ref="A1:AP92">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13677,7 +13550,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI92">
+  <conditionalFormatting sqref="A2:AI91">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
